--- a/WorkBot/refactor-experimental/data/orders/Regional Access Inc/Regional Access Inc._Bakery_20251110.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Regional Access Inc/Regional Access Inc._Bakery_20251110.xlsx
@@ -450,20 +450,14 @@
           <t>Chocolate - Unsweetened Dark</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>598.75</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>598.75</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>598.75</v>
+      </c>
+      <c r="E2" t="n">
+        <v>598.75</v>
       </c>
     </row>
   </sheetData>
